--- a/fix-invariant/ig/StructureDefinition-tddui-task-transport.xlsx
+++ b/fix-invariant/ig/StructureDefinition-tddui-task-transport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T12:11:00+00:00</t>
+    <t>2026-07-16T12:36:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-invariant/ig/StructureDefinition-tddui-task-transport.xlsx
+++ b/fix-invariant/ig/StructureDefinition-tddui-task-transport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T12:36:44+00:00</t>
+    <t>2026-07-16T13:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-invariant/ig/StructureDefinition-tddui-task-transport.xlsx
+++ b/fix-invariant/ig/StructureDefinition-tddui-task-transport.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T13:49:33+00:00</t>
+    <t>2026-07-16T14:55:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-invariant/ig/StructureDefinition-tddui-task-transport.xlsx
+++ b/fix-invariant/ig/StructureDefinition-tddui-task-transport.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.4.0-ballot</t>
+    <t>2.4.0-tru</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:57:40+00:00</t>
+    <t>2026-07-23T07:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
